--- a/test-cases/Sample_Test_Cases.xlsx
+++ b/test-cases/Sample_Test_Cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/FB7F8EA46265AFCE/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb7f8ea46265afce/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B421E42D-9F4E-4AE7-971F-3B75A61C1C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{452E0F0F-084A-4F4E-9280-5E15F34A30E5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{B421E42D-9F4E-4AE7-971F-3B75A61C1C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53B8D2E0-1A6B-4937-AACE-8E2728DE8A72}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1136,7 +1136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1755,7 +1755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -1770,20 +1770,20 @@
     <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24" customHeight="1">
+    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="6" customHeight="1">
+    <row r="3" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="21.75" customHeight="1">
+    <row r="4" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18" customHeight="1">
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>14</v>
       </c>
@@ -1837,7 +1837,7 @@
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
     </row>
-    <row r="6" spans="1:12" ht="54.75" customHeight="1">
+    <row r="6" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>15</v>
       </c>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="L6" s="29"/>
     </row>
-    <row r="7" spans="1:12" ht="54.75" customHeight="1">
+    <row r="7" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>25</v>
       </c>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="1:12" ht="54.75" customHeight="1">
+    <row r="8" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>33</v>
       </c>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="L8" s="29"/>
     </row>
-    <row r="9" spans="1:12" ht="54.75" customHeight="1">
+    <row r="9" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
         <v>40</v>
       </c>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="1:12" ht="54.75" customHeight="1">
+    <row r="10" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>45</v>
       </c>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="L10" s="29"/>
     </row>
-    <row r="11" spans="1:12" ht="54.75" customHeight="1">
+    <row r="11" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
         <v>52</v>
       </c>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="1:12" ht="54.75" customHeight="1">
+    <row r="12" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>57</v>
       </c>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="L12" s="29"/>
     </row>
-    <row r="13" spans="1:12" ht="54.75" customHeight="1">
+    <row r="13" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>66</v>
       </c>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="1:12" ht="18" customHeight="1">
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
         <v>71</v>
       </c>
@@ -2141,7 +2141,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="24"/>
     </row>
-    <row r="15" spans="1:12" ht="54.75" customHeight="1">
+    <row r="15" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>72</v>
       </c>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="1:12" ht="54.75" customHeight="1">
+    <row r="16" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>78</v>
       </c>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L16" s="29"/>
     </row>
-    <row r="17" spans="1:12" ht="54.75" customHeight="1">
+    <row r="17" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>85</v>
       </c>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="1:12" ht="54.75" customHeight="1">
+    <row r="18" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>91</v>
       </c>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="L18" s="29"/>
     </row>
-    <row r="19" spans="1:12" ht="54.75" customHeight="1">
+    <row r="19" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
         <v>98</v>
       </c>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="1:12" ht="54.75" customHeight="1">
+    <row r="20" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>103</v>
       </c>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" spans="1:12" ht="54.75" customHeight="1">
+    <row r="21" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>109</v>
       </c>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="1:12" ht="18" customHeight="1">
+    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
         <v>115</v>
       </c>
@@ -2407,7 +2407,7 @@
       <c r="K22" s="24"/>
       <c r="L22" s="24"/>
     </row>
-    <row r="23" spans="1:12" ht="54.75" customHeight="1">
+    <row r="23" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="32" t="s">
         <v>116</v>
       </c>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="1:12" ht="54.75" customHeight="1">
+    <row r="24" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>123</v>
       </c>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="L24" s="29"/>
     </row>
-    <row r="25" spans="1:12" ht="54.75" customHeight="1">
+    <row r="25" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
         <v>127</v>
       </c>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="1:12" ht="54.75" customHeight="1">
+    <row r="26" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>134</v>
       </c>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="L26" s="29"/>
     </row>
-    <row r="27" spans="1:12" ht="54.75" customHeight="1">
+    <row r="27" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>140</v>
       </c>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L27" s="34"/>
     </row>
-    <row r="28" spans="1:12" ht="54.75" customHeight="1">
+    <row r="28" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
         <v>145</v>
       </c>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="L28" s="29"/>
     </row>
-    <row r="29" spans="1:12" ht="18" customHeight="1">
+    <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="43" t="s">
         <v>150</v>
       </c>
@@ -2639,7 +2639,7 @@
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
     </row>
-    <row r="30" spans="1:12" ht="54.75" customHeight="1">
+    <row r="30" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
         <v>151</v>
       </c>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="L30" s="29"/>
     </row>
-    <row r="31" spans="1:12" ht="54.75" customHeight="1">
+    <row r="31" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32" t="s">
         <v>157</v>
       </c>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="L31" s="34"/>
     </row>
-    <row r="32" spans="1:12" ht="54.75" customHeight="1">
+    <row r="32" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
         <v>163</v>
       </c>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="L32" s="29"/>
     </row>
-    <row r="33" spans="1:12" ht="54.75" customHeight="1">
+    <row r="33" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
         <v>169</v>
       </c>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="L33" s="34"/>
     </row>
-    <row r="34" spans="1:12" ht="54.75" customHeight="1">
+    <row r="34" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>175</v>
       </c>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="L34" s="29"/>
     </row>
-    <row r="35" spans="1:12" ht="54.75" customHeight="1">
+    <row r="35" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="32" t="s">
         <v>181</v>
       </c>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L35" s="34"/>
     </row>
-    <row r="36" spans="1:12" ht="18" customHeight="1">
+    <row r="36" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
         <v>186</v>
       </c>
@@ -2869,7 +2869,7 @@
       <c r="K36" s="24"/>
       <c r="L36" s="24"/>
     </row>
-    <row r="37" spans="1:12" ht="54.75" customHeight="1">
+    <row r="37" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="32" t="s">
         <v>187</v>
       </c>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="L37" s="34"/>
     </row>
-    <row r="38" spans="1:12" ht="54.75" customHeight="1">
+    <row r="38" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
         <v>194</v>
       </c>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L38" s="29"/>
     </row>
-    <row r="39" spans="1:12" ht="54.75" customHeight="1">
+    <row r="39" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32" t="s">
         <v>199</v>
       </c>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L39" s="34"/>
     </row>
-    <row r="40" spans="1:12" ht="54.75" customHeight="1">
+    <row r="40" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>206</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="L40" s="29"/>
     </row>
-    <row r="41" spans="1:12" ht="54.75" customHeight="1">
+    <row r="41" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
         <v>212</v>
       </c>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="L41" s="34"/>
     </row>
-    <row r="42" spans="1:12" ht="54.75" customHeight="1">
+    <row r="42" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
         <v>218</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="L42" s="29"/>
     </row>
-    <row r="43" spans="1:12" ht="18" customHeight="1">
+    <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
         <v>224</v>
       </c>
@@ -3101,7 +3101,7 @@
       <c r="K43" s="24"/>
       <c r="L43" s="24"/>
     </row>
-    <row r="44" spans="1:12" ht="54.75" customHeight="1">
+    <row r="44" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="27" t="s">
         <v>225</v>
       </c>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="L44" s="29"/>
     </row>
-    <row r="45" spans="1:12" ht="54.75" customHeight="1">
+    <row r="45" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32" t="s">
         <v>232</v>
       </c>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="L45" s="34"/>
     </row>
-    <row r="46" spans="1:12" ht="54.75" customHeight="1">
+    <row r="46" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="27" t="s">
         <v>238</v>
       </c>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="L46" s="29"/>
     </row>
-    <row r="47" spans="1:12" ht="54.75" customHeight="1">
+    <row r="47" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="32" t="s">
         <v>244</v>
       </c>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="L47" s="34"/>
     </row>
-    <row r="48" spans="1:12" ht="54.75" customHeight="1">
+    <row r="48" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
         <v>249</v>
       </c>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L48" s="29"/>
     </row>
-    <row r="49" spans="1:12" ht="54.75" customHeight="1">
+    <row r="49" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32" t="s">
         <v>254</v>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="L49" s="34"/>
     </row>
-    <row r="50" spans="1:12" ht="54.75" customHeight="1">
+    <row r="50" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
         <v>260</v>
       </c>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="L50" s="29"/>
     </row>
-    <row r="51" spans="1:12" ht="54.75" customHeight="1">
+    <row r="51" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="32" t="s">
         <v>265</v>
       </c>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="L51" s="34"/>
     </row>
-    <row r="52" spans="1:12" ht="54.75" customHeight="1">
+    <row r="52" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
         <v>271</v>
       </c>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="L52" s="29"/>
     </row>
-    <row r="53" spans="1:12" ht="54.75" customHeight="1">
+    <row r="53" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="32" t="s">
         <v>277</v>
       </c>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="L53" s="34"/>
     </row>
-    <row r="54" spans="1:12" ht="54.75" customHeight="1">
+    <row r="54" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
         <v>284</v>
       </c>
@@ -3509,7 +3509,7 @@
     <tabColor rgb="FF2D3250"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -3518,17 +3518,17 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" customHeight="1">
+    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21.75" customHeight="1">
+    <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>71</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="19.5" customHeight="1">
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>115</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="19.5" customHeight="1">
+    <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="19.5" customHeight="1">
+    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>186</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="19.5" customHeight="1">
+    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>224</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>0.36363636363636365</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="19.5" customHeight="1">
+    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>293</v>
       </c>
@@ -3790,7 +3790,7 @@
     <tabColor rgb="FF7B241C"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -3802,13 +3802,13 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="3.75" customHeight="1"/>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1">
+    <row r="2" spans="1:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>295</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="39.75" customHeight="1">
+    <row r="4" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -3852,7 +3852,7 @@
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
     </row>
-    <row r="5" spans="1:10" ht="39.75" customHeight="1">
+    <row r="5" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20"/>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -3864,7 +3864,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="20"/>
     </row>
-    <row r="6" spans="1:10" ht="39.75" customHeight="1">
+    <row r="6" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3876,7 +3876,7 @@
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
     </row>
-    <row r="7" spans="1:10" ht="39.75" customHeight="1">
+    <row r="7" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -3888,7 +3888,7 @@
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
     </row>
-    <row r="8" spans="1:10" ht="39.75" customHeight="1">
+    <row r="8" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -3900,7 +3900,7 @@
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
     </row>
-    <row r="9" spans="1:10" ht="39.75" customHeight="1">
+    <row r="9" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3912,7 +3912,7 @@
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
     </row>
-    <row r="10" spans="1:10" ht="39.75" customHeight="1">
+    <row r="10" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3924,7 +3924,7 @@
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
     </row>
-    <row r="11" spans="1:10" ht="39.75" customHeight="1">
+    <row r="11" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -3936,7 +3936,7 @@
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
     </row>
-    <row r="12" spans="1:10" ht="39.75" customHeight="1">
+    <row r="12" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -3948,7 +3948,7 @@
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
     </row>
-    <row r="13" spans="1:10" ht="39.75" customHeight="1">
+    <row r="13" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -3960,7 +3960,7 @@
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" spans="1:10" ht="39.75" customHeight="1">
+    <row r="14" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -3972,7 +3972,7 @@
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
     </row>
-    <row r="15" spans="1:10" ht="39.75" customHeight="1">
+    <row r="15" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -3984,7 +3984,7 @@
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" ht="39.75" customHeight="1">
+    <row r="16" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -3996,7 +3996,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="19"/>
     </row>
-    <row r="17" spans="1:10" ht="39.75" customHeight="1">
+    <row r="17" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -4008,7 +4008,7 @@
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="1:10" ht="39.75" customHeight="1">
+    <row r="18" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -4020,7 +4020,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
     </row>
-    <row r="19" spans="1:10" ht="39.75" customHeight="1">
+    <row r="19" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -4032,7 +4032,7 @@
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="39.75" customHeight="1">
+    <row r="20" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -4044,7 +4044,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
     </row>
-    <row r="21" spans="1:10" ht="39.75" customHeight="1">
+    <row r="21" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20"/>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -4056,7 +4056,7 @@
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" ht="39.75" customHeight="1">
+    <row r="22" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -4068,7 +4068,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="19"/>
     </row>
-    <row r="23" spans="1:10" ht="39.75" customHeight="1">
+    <row r="23" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -4092,7 +4092,7 @@
     <tabColor rgb="FF1A5276"/>
   </sheetPr>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -4104,13 +4104,13 @@
     <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
+    <row r="1" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="3.75" customHeight="1"/>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1">
+    <row r="2" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>304</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="39.75" customHeight="1">
+    <row r="4" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>231</v>
       </c>
@@ -4156,7 +4156,7 @@
       <c r="H4" s="16"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" ht="39.75" customHeight="1">
+    <row r="5" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>237</v>
       </c>
@@ -4173,7 +4173,7 @@
       <c r="H5" s="12"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="39.75" customHeight="1">
+    <row r="6" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>243</v>
       </c>
@@ -4190,7 +4190,7 @@
       <c r="H6" s="16"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9" ht="39.75" customHeight="1">
+    <row r="7" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>133</v>
       </c>
@@ -4207,7 +4207,7 @@
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="39.75" customHeight="1">
+    <row r="8" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>193</v>
       </c>
@@ -4224,7 +4224,7 @@
       <c r="H8" s="16"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" ht="39.75" customHeight="1">
+    <row r="9" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>259</v>
       </c>
@@ -4241,7 +4241,7 @@
       <c r="H9" s="12"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="39.75" customHeight="1">
+    <row r="10" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>84</v>
       </c>
@@ -4258,7 +4258,7 @@
       <c r="H10" s="16"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="39.75" customHeight="1">
+    <row r="11" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>270</v>
       </c>
@@ -4275,7 +4275,7 @@
       <c r="H11" s="12"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="39.75" customHeight="1">
+    <row r="12" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>276</v>
       </c>
